--- a/reviews/a-envoyer/gossip-beauty-center-2026-09-07.xlsx
+++ b/reviews/a-envoyer/gossip-beauty-center-2026-09-07.xlsx
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T06:06:08</t>
+          <t>2026-09-04T09:25:00</t>
         </is>
       </c>
     </row>
